--- a/Masterlist 2027-2028_Mau_moi.xlsx
+++ b/Masterlist 2027-2028_Mau_moi.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hntna\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\QHDC3\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="0" windowWidth="19200" windowHeight="7050" tabRatio="881"/>
+    <workbookView xWindow="2790" yWindow="0" windowWidth="19200" windowHeight="7050" tabRatio="881"/>
   </bookViews>
   <sheets>
     <sheet name="PL1.1 ML2027-2028" sheetId="1" r:id="rId1"/>
@@ -954,7 +954,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="38">
   <si>
     <t>TT</t>
   </si>
@@ -972,9 +972,6 @@
   </si>
   <si>
     <t>VT</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <t>II</t>
@@ -998,13 +995,7 @@
     <t>Mã loại</t>
   </si>
   <si>
-    <t>5G</t>
-  </si>
-  <si>
     <t>P1</t>
-  </si>
-  <si>
-    <t>VTTB</t>
   </si>
   <si>
     <t>Mạng 5G</t>
@@ -1013,16 +1004,7 @@
     <t>Đơn giá dự kiến</t>
   </si>
   <si>
-    <t>VPDĐ</t>
-  </si>
-  <si>
-    <t>DLDĐ</t>
-  </si>
-  <si>
     <t>KHÔNG XÓA</t>
-  </si>
-  <si>
-    <t>VHKT</t>
   </si>
   <si>
     <t>Thành tiền dự kiến (VNĐ)</t>
@@ -1031,13 +1013,7 @@
     <t>Dự kiến đơn vị đầu tư, mua sắm</t>
   </si>
   <si>
-    <t>PCTT</t>
-  </si>
-  <si>
     <t>Đảm bảo dự phòng ƯCTT</t>
-  </si>
-  <si>
-    <t>ƯCTT</t>
   </si>
   <si>
     <t>TỔNG ĐẦU TƯ VTTB VÀ XÂY LẮP 2027-2028</t>
@@ -1073,55 +1049,10 @@
     <t>1</t>
   </si>
   <si>
-    <t>Thiết bị macro 5G</t>
-  </si>
-  <si>
-    <t>Huawei_eNodeB 32T32R Dualband 2600-3500MHz (3AAU 3 sector, 3 cell LTE TDD @20+20+20MHz per 1 sector  band 2600MHz and 1 cell NR @100MHz per 1 sector band C), Excluse BBU box.</t>
-  </si>
-  <si>
-    <t>Trạm</t>
-  </si>
-  <si>
-    <t>NodeB Massive MIMO 2.6GHz+3.5GHz</t>
-  </si>
-  <si>
-    <t>Tủ</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
-    <t>Thiết bị RRU 5G</t>
-  </si>
-  <si>
-    <t>RRU 5G triển khai IBD</t>
-  </si>
-  <si>
-    <t>Chiếc</t>
-  </si>
-  <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>Thiết bị smallcell 5G</t>
-  </si>
-  <si>
-    <t>Thiết bị vô tuyến 5G 4T4R</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Card Baseband</t>
-  </si>
-  <si>
-    <t>Card Baseband cho 5G</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Nâng cấp hệ thống Inbuilding lên 5G</t>
   </si>
   <si>
     <t>A2</t>
@@ -1133,148 +1064,22 @@
     <t>Thiết bị 4G</t>
   </si>
   <si>
-    <t>Huawei_SRAN Tripband eNodeB 700+800+900MHz (3 RRU 4x120w)(L111@15MHz+L111@10MHz ) 12Trx. Exclude BBU + BB card</t>
-  </si>
-  <si>
-    <t>Huawei_SRAN Tripband eNodeB 700+800+900MHz (3 RRU 4x120w)(L111@15MHz+L111@10MHz , 12TRx, BB card UBBPg2a) + 3 AISG</t>
-  </si>
-  <si>
-    <t>ZTE_SRAN Tripband eNodeB 700+800+900MHz (3 RRU 4x120w)(L111@15MHz+L111@10MHz , 12TRx, excluse BBU + BB card</t>
-  </si>
-  <si>
-    <t>ZTE_SRAN Tripband eNodeB 700+800+900MHz (3 RRU 4x120w)(L111@15MHz+L111@10MHz , 12TRx, BB VBPe3p)</t>
-  </si>
-  <si>
-    <t>Anten 4G 8 port 4 port 700-900 + 4P 1800-2600 MHz</t>
-  </si>
-  <si>
-    <t>Jumper</t>
-  </si>
-  <si>
-    <t>Bộ Gá đa năng (gồm 3 gá đơn lẻ và các phụ kiện)</t>
-  </si>
-  <si>
     <t>Thiết bị 3G</t>
-  </si>
-  <si>
-    <t>NodeB 3G dualband_Cosite</t>
-  </si>
-  <si>
-    <t>NodeB 3G dualband_New site</t>
-  </si>
-  <si>
-    <t>Card baseband</t>
-  </si>
-  <si>
-    <t>Anten đa băng</t>
   </si>
   <si>
     <t>Thiết bị 2G</t>
   </si>
   <si>
-    <t>BTS 2G dualband_Cosite</t>
-  </si>
-  <si>
-    <t>BTS 2G dualband_New site 2G</t>
-  </si>
-  <si>
     <t>Dung lượng</t>
-  </si>
-  <si>
-    <t>Huawei_SRAN dual band 1800-2100Mhz (3RRU 4T4R - 120W, L111@20MHz+L111@10MHz, 12TRx, BBU + BB UBBPh3a)</t>
-  </si>
-  <si>
-    <t>Huawei_SRAN dual band 1800-2100Mhz (3RRU 4T4R - 120W, L111@20MHz+L111@10MHz, 12TRx, Excluse Baseband and BB card)</t>
-  </si>
-  <si>
-    <t>Huawei_eNodeB 8T8R 2600MHz (3 RRU 9 cell @20+20+20MHz) Excluse BBU and BB card</t>
-  </si>
-  <si>
-    <t>ZTE_SRAN dual band 1800-2100Mhz (3RRU 4T4R - 120W, L111@20MHz+L222@10MHz, U333, 12TRx + BB VBPe3p, Excluse BBU box)</t>
-  </si>
-  <si>
-    <t>ZTE_SRAN dual band 1800-2100Mhz (3RRU 4T4R - 120W, L111@20MHz+L222@10MHz, U333, 12TRx) Excluse BBU box and BB card</t>
-  </si>
-  <si>
-    <t>ZTE_eNodeB 32T32R Dualband 2600-3500MHz (3AAU 3 sector, 3 cell LTE TDD @20+20+20MHz per 1 sector  band 2600MHz and 1 cell NR @100MHz per 1 sector band C), Excluse BBU box.</t>
-  </si>
-  <si>
-    <t>eNodeB 8T8R 2600MHz (3 RRU 9 cell @20+20+20MHz) Excluse BBU and BB card</t>
-  </si>
-  <si>
-    <t>Cái</t>
-  </si>
-  <si>
-    <t>BTS 2G 1800_Cosite</t>
-  </si>
-  <si>
-    <t>BTS 2G 900_Cosite</t>
   </si>
   <si>
     <t>Hiện đại hóa mạng lưới</t>
   </si>
   <si>
-    <t>Swap 2100Mhz_sector</t>
-  </si>
-  <si>
-    <t>Bộ</t>
-  </si>
-  <si>
     <t>Nâng cao chất lượng mạng</t>
   </si>
   <si>
-    <t>Phần mềm, công cụ</t>
-  </si>
-  <si>
-    <t>Nâng cấp softwrae 2G</t>
-  </si>
-  <si>
-    <t>Package</t>
-  </si>
-  <si>
-    <t>Nâng cấp softwrae 4G</t>
-  </si>
-  <si>
-    <t>Tính năng mới</t>
-  </si>
-  <si>
-    <t>Service deploy BSC,  RNC (Huawei)</t>
-  </si>
-  <si>
-    <t>Dịch vụ triển khai OMC</t>
-  </si>
-  <si>
-    <t>BSC6910 (GSM: 2048) (SW) License</t>
-  </si>
-  <si>
-    <t>NDS + NGI ZTE</t>
-  </si>
-  <si>
-    <t>pcs</t>
-  </si>
-  <si>
-    <t>Xe cơ động phục vụ LHSK</t>
-  </si>
-  <si>
-    <t>Xe phát sóng cơ động</t>
-  </si>
-  <si>
-    <t>Xe phát sóng chỉ huy, dã chiến đảm bảo hoạt động liên tục trong thiên tai, địch họa</t>
-  </si>
-  <si>
     <t>A3</t>
-  </si>
-  <si>
-    <t>Huawei_RRU Tripband 700-800-900MHz 120W 4T4R</t>
-  </si>
-  <si>
-    <t>Huawei_RRU dualband 1800-2100MHz 120W 4T4R</t>
-  </si>
-  <si>
-    <t>ZTE_RRU Tripband 700-800-900MHz 120W 4T4R</t>
-  </si>
-  <si>
-    <t>ZTE_RRU dualband 1800-2100MHz 120W 4T4R</t>
   </si>
 </sst>
 </file>
@@ -1285,13 +1090,13 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₫_-;\-* #,##0.00\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="[$-409]dd\-mmm\-yy;@"/>
-    <numFmt numFmtId="171" formatCode="_([$€-2]* #,##0.00_);_([$€-2]* \(#,##0.00\);_([$€-2]* &quot;-&quot;??_)"/>
-    <numFmt numFmtId="172" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="173" formatCode="_(* #.##0.00_);_(* \(#.##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="175" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_([$€-2]* #.##0.00_);_([$€-2]* \(#.##0.00\);_([$€-2]* &quot;-&quot;??_)"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="[$-409]dd\-mmm\-yy;@"/>
+    <numFmt numFmtId="168" formatCode="_([$€-2]* #,##0.00_);_([$€-2]* \(#,##0.00\);_([$€-2]* &quot;-&quot;??_)"/>
+    <numFmt numFmtId="169" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="_(* #.##0.00_);_(* \(#.##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="171" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="172" formatCode="_([$€-2]* #.##0.00_);_([$€-2]* \(#.##0.00\);_([$€-2]* &quot;-&quot;??_)"/>
   </numFmts>
   <fonts count="30" x14ac:knownFonts="1">
     <font>
@@ -1673,7 +1478,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="top"/>
     </xf>
@@ -1694,13 +1499,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
@@ -1711,7 +1516,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="top"/>
     </xf>
@@ -1728,13 +1533,13 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="14" fillId="0" borderId="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
@@ -1752,7 +1557,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
@@ -1954,24 +1759,24 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="173" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
@@ -1982,7 +1787,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2259,14 +2064,19 @@
     <xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="28" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2336,14 +2146,6 @@
     </xf>
     <xf numFmtId="165" fontId="24" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="287">
@@ -2922,7 +2724,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q93"/>
+  <dimension ref="A1:Q85"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="12.75" outlineLevelRow="4" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="5" customWidth="1"/>
@@ -2945,28 +2747,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="99" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
+      <c r="A1" s="100" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
       <c r="N1" s="4"/>
       <c r="O1" s="4"/>
-      <c r="P1" s="114"/>
+      <c r="P1" s="92"/>
     </row>
     <row r="2" spans="1:17" s="22" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="93"/>
-      <c r="B2" s="93"/>
+      <c r="A2" s="94"/>
+      <c r="B2" s="94"/>
       <c r="C2" s="12"/>
       <c r="D2" s="13"/>
       <c r="E2" s="13"/>
@@ -2980,94 +2782,94 @@
       <c r="M2" s="20"/>
       <c r="N2" s="20"/>
       <c r="O2" s="21"/>
-      <c r="P2" s="115"/>
+      <c r="P2" s="93"/>
       <c r="Q2" s="19"/>
     </row>
     <row r="3" spans="1:17" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="94"/>
-      <c r="B3" s="94"/>
+      <c r="A3" s="95"/>
+      <c r="B3" s="95"/>
       <c r="C3" s="16"/>
       <c r="D3" s="17"/>
       <c r="E3" s="17"/>
       <c r="F3" s="14"/>
-      <c r="G3" s="106" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="106"/>
+      <c r="G3" s="107" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="107"/>
       <c r="I3" s="18"/>
-      <c r="J3" s="95" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="95"/>
-      <c r="L3" s="95"/>
+      <c r="J3" s="96" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="96"/>
+      <c r="L3" s="96"/>
       <c r="M3" s="20"/>
       <c r="N3" s="20"/>
       <c r="O3" s="24"/>
-      <c r="P3" s="115"/>
+      <c r="P3" s="93"/>
       <c r="Q3" s="23"/>
     </row>
     <row r="4" spans="1:17" s="30" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="100" t="s">
+      <c r="A4" s="101" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="100" t="s">
+      <c r="B4" s="101" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="103" t="s">
+      <c r="C4" s="104" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="107" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="108"/>
-      <c r="F4" s="111" t="s">
+      <c r="D4" s="108" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="109"/>
+      <c r="F4" s="112" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="114" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="114"/>
+      <c r="I4" s="97" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="113" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="113"/>
-      <c r="I4" s="96" t="s">
-        <v>24</v>
-      </c>
       <c r="J4" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="27" t="s">
+      <c r="L4" s="27" t="s">
         <v>12</v>
-      </c>
-      <c r="L4" s="27" t="s">
-        <v>13</v>
       </c>
       <c r="M4" s="28"/>
       <c r="N4" s="28"/>
       <c r="O4" s="28"/>
-      <c r="P4" s="115"/>
+      <c r="P4" s="93"/>
       <c r="Q4" s="29"/>
     </row>
     <row r="5" spans="1:17" s="30" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="101"/>
-      <c r="B5" s="101"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="109"/>
-      <c r="E5" s="110"/>
-      <c r="F5" s="112"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="97"/>
+      <c r="A5" s="102"/>
+      <c r="B5" s="102"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="111"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="114"/>
+      <c r="I5" s="98"/>
       <c r="J5" s="27"/>
       <c r="K5" s="27"/>
       <c r="L5" s="27"/>
       <c r="M5" s="28"/>
       <c r="N5" s="28"/>
       <c r="O5" s="28"/>
-      <c r="P5" s="115"/>
+      <c r="P5" s="93"/>
       <c r="Q5" s="29"/>
     </row>
     <row r="6" spans="1:17" s="30" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" s="102"/>
-      <c r="B6" s="102"/>
-      <c r="C6" s="105"/>
+      <c r="A6" s="103"/>
+      <c r="B6" s="103"/>
+      <c r="C6" s="106"/>
       <c r="D6" s="31">
         <v>2027</v>
       </c>
@@ -3083,14 +2885,14 @@
       <c r="H6" s="31">
         <v>2028</v>
       </c>
-      <c r="I6" s="97"/>
+      <c r="I6" s="98"/>
       <c r="J6" s="27"/>
       <c r="K6" s="27"/>
       <c r="L6" s="27"/>
       <c r="M6" s="28"/>
       <c r="N6" s="28"/>
       <c r="O6" s="28"/>
-      <c r="P6" s="115"/>
+      <c r="P6" s="93"/>
       <c r="Q6" s="29"/>
     </row>
     <row r="7" spans="1:17" s="39" customFormat="1" ht="15" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -3105,39 +2907,39 @@
         <v>7</v>
       </c>
       <c r="G7" s="37">
-        <f>SUBTOTAL(9,G8:G93)</f>
-        <v>6703944.7016552296</v>
+        <f>SUBTOTAL(9,G8:G85)</f>
+        <v>0</v>
       </c>
       <c r="H7" s="37">
-        <f>SUBTOTAL(9,H8:H93)</f>
-        <v>6963516.8190324334</v>
-      </c>
-      <c r="I7" s="98"/>
+        <f>SUBTOTAL(9,H8:H85)</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="99"/>
       <c r="J7" s="28"/>
       <c r="K7" s="28"/>
       <c r="L7" s="28"/>
       <c r="M7" s="28"/>
       <c r="N7" s="28"/>
       <c r="O7" s="28"/>
-      <c r="P7" s="115"/>
+      <c r="P7" s="93"/>
       <c r="Q7" s="38"/>
     </row>
     <row r="8" spans="1:17" s="49" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="40"/>
       <c r="B8" s="41" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C8" s="40"/>
       <c r="D8" s="42"/>
       <c r="E8" s="42"/>
       <c r="F8" s="42"/>
       <c r="G8" s="43">
-        <f>SUBTOTAL(9,G9:G93)</f>
-        <v>6703944.7016552296</v>
+        <f>SUBTOTAL(9,G9:G85)</f>
+        <v>0</v>
       </c>
       <c r="H8" s="43">
-        <f>SUBTOTAL(9,H9:H93)</f>
-        <v>6963516.8190324334</v>
+        <f>SUBTOTAL(9,H9:H85)</f>
+        <v>0</v>
       </c>
       <c r="I8" s="44"/>
       <c r="J8" s="45"/>
@@ -3151,22 +2953,22 @@
     </row>
     <row r="9" spans="1:17" s="49" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="50" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B9" s="51" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C9" s="52"/>
       <c r="D9" s="53"/>
       <c r="E9" s="53"/>
       <c r="F9" s="53"/>
       <c r="G9" s="54">
-        <f>SUBTOTAL(9,G10:G93)</f>
-        <v>6703944.7016552296</v>
+        <f>SUBTOTAL(9,G10:G85)</f>
+        <v>0</v>
       </c>
       <c r="H9" s="54">
-        <f>SUBTOTAL(9,H10:H93)</f>
-        <v>6963516.8190324334</v>
+        <f>SUBTOTAL(9,H10:H85)</f>
+        <v>0</v>
       </c>
       <c r="I9" s="54"/>
       <c r="J9" s="28"/>
@@ -3180,18 +2982,18 @@
     </row>
     <row r="10" spans="1:17" s="59" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="55" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="56" t="s">
-        <v>9</v>
-      </c>
       <c r="G10" s="65">
-        <f>SUBTOTAL(9,G11:G93)</f>
-        <v>6703944.7016552296</v>
+        <f>SUBTOTAL(9,G11:G85)</f>
+        <v>0</v>
       </c>
       <c r="H10" s="65">
-        <f>SUBTOTAL(9,H11:H93)</f>
-        <v>6963516.8190324334</v>
+        <f>SUBTOTAL(9,H11:H85)</f>
+        <v>0</v>
       </c>
       <c r="J10" s="57" t="s">
         <v>5</v>
@@ -3199,10 +3001,10 @@
     </row>
     <row r="11" spans="1:17" s="58" customFormat="1" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A11" s="66" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B11" s="67" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C11" s="68"/>
       <c r="D11" s="69"/>
@@ -3222,268 +3024,134 @@
       <c r="L11" s="38"/>
     </row>
     <row r="12" spans="1:17" s="72" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A12" s="66" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="64" t="s">
-        <v>35</v>
-      </c>
+      <c r="A12" s="66"/>
+      <c r="B12" s="64"/>
       <c r="C12" s="68"/>
       <c r="D12" s="69"/>
       <c r="E12" s="69"/>
       <c r="F12" s="69"/>
-      <c r="G12" s="69">
-        <f>SUBTOTAL(9,G13:G14)</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="69">
-        <f>SUBTOTAL(9,H13:H14)</f>
-        <v>0</v>
-      </c>
+      <c r="G12" s="69"/>
+      <c r="H12" s="69"/>
       <c r="I12" s="70"/>
       <c r="J12" s="71"/>
       <c r="K12" s="71"/>
       <c r="L12" s="71"/>
     </row>
     <row r="13" spans="1:17" s="72" customFormat="1" ht="42" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A13" s="66" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="88" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="74" t="s">
-        <v>37</v>
-      </c>
+      <c r="A13" s="66"/>
+      <c r="B13" s="88"/>
+      <c r="C13" s="74"/>
       <c r="D13" s="75"/>
       <c r="E13" s="75"/>
       <c r="F13" s="75"/>
-      <c r="G13" s="75">
-        <f>F13*D13</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="75">
-        <f>F13*E13</f>
-        <v>0</v>
-      </c>
+      <c r="G13" s="75"/>
+      <c r="H13" s="75"/>
       <c r="I13" s="76"/>
-      <c r="J13" s="71" t="s">
-        <v>5</v>
-      </c>
-      <c r="K13" s="71" t="s">
-        <v>14</v>
-      </c>
-      <c r="L13" s="71" t="s">
-        <v>16</v>
-      </c>
+      <c r="J13" s="71"/>
+      <c r="K13" s="71"/>
+      <c r="L13" s="71"/>
     </row>
     <row r="14" spans="1:17" s="72" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A14" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="63" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="78" t="s">
-        <v>39</v>
-      </c>
+      <c r="A14" s="77"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="78"/>
       <c r="D14" s="75"/>
       <c r="E14" s="75"/>
       <c r="F14" s="75"/>
-      <c r="G14" s="75">
-        <f>F14*D14</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="75">
-        <f>F14*E14</f>
-        <v>0</v>
-      </c>
+      <c r="G14" s="75"/>
+      <c r="H14" s="75"/>
       <c r="I14" s="76"/>
-      <c r="J14" s="71" t="s">
-        <v>5</v>
-      </c>
-      <c r="K14" s="71" t="s">
-        <v>14</v>
-      </c>
-      <c r="L14" s="71" t="s">
-        <v>16</v>
-      </c>
+      <c r="J14" s="71"/>
+      <c r="K14" s="71"/>
+      <c r="L14" s="71"/>
     </row>
     <row r="15" spans="1:17" s="72" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A15" s="66" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="64" t="s">
-        <v>41</v>
-      </c>
+      <c r="A15" s="66"/>
+      <c r="B15" s="64"/>
       <c r="C15" s="74"/>
       <c r="D15" s="75"/>
       <c r="E15" s="75"/>
       <c r="F15" s="75"/>
-      <c r="G15" s="75">
-        <f>SUBTOTAL(9,G16:G16)</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="75">
-        <f>SUBTOTAL(9,H16:H16)</f>
-        <v>0</v>
-      </c>
+      <c r="G15" s="75"/>
+      <c r="H15" s="75"/>
       <c r="I15" s="76"/>
       <c r="J15" s="71"/>
       <c r="K15" s="71"/>
       <c r="L15" s="71"/>
     </row>
     <row r="16" spans="1:17" s="72" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A16" s="66" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="73" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="74" t="s">
-        <v>43</v>
-      </c>
+      <c r="A16" s="66"/>
+      <c r="B16" s="73"/>
+      <c r="C16" s="74"/>
       <c r="D16" s="75"/>
       <c r="E16" s="75"/>
       <c r="F16" s="75"/>
-      <c r="G16" s="75">
-        <f>F16*D16</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="75">
-        <f>F16*E16</f>
-        <v>0</v>
-      </c>
+      <c r="G16" s="75"/>
+      <c r="H16" s="75"/>
       <c r="I16" s="76"/>
-      <c r="J16" s="71" t="s">
-        <v>5</v>
-      </c>
-      <c r="K16" s="71" t="s">
-        <v>14</v>
-      </c>
-      <c r="L16" s="71" t="s">
-        <v>16</v>
-      </c>
+      <c r="J16" s="71"/>
+      <c r="K16" s="71"/>
+      <c r="L16" s="71"/>
     </row>
     <row r="17" spans="1:12" s="72" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A17" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="64" t="s">
-        <v>45</v>
-      </c>
+      <c r="A17" s="66"/>
+      <c r="B17" s="64"/>
       <c r="C17" s="68"/>
       <c r="D17" s="69"/>
       <c r="E17" s="69"/>
       <c r="F17" s="69"/>
-      <c r="G17" s="69">
-        <f>SUBTOTAL(9,G18:G18)</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="69">
-        <f>SUBTOTAL(9,H18:H18)</f>
-        <v>0</v>
-      </c>
+      <c r="G17" s="69"/>
+      <c r="H17" s="69"/>
       <c r="I17" s="70"/>
       <c r="J17" s="71"/>
       <c r="K17" s="71"/>
       <c r="L17" s="71"/>
     </row>
     <row r="18" spans="1:12" s="72" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A18" s="66" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="73" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="74" t="s">
-        <v>43</v>
-      </c>
+      <c r="A18" s="66"/>
+      <c r="B18" s="73"/>
+      <c r="C18" s="74"/>
       <c r="D18" s="75"/>
       <c r="E18" s="79"/>
       <c r="F18" s="75"/>
-      <c r="G18" s="75">
-        <f>F18*D18</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="75">
-        <f>F18*E18</f>
-        <v>0</v>
-      </c>
+      <c r="G18" s="75"/>
+      <c r="H18" s="75"/>
       <c r="I18" s="76"/>
-      <c r="J18" s="71" t="s">
-        <v>5</v>
-      </c>
-      <c r="K18" s="71" t="s">
-        <v>14</v>
-      </c>
-      <c r="L18" s="71" t="s">
-        <v>16</v>
-      </c>
+      <c r="J18" s="71"/>
+      <c r="K18" s="71"/>
+      <c r="L18" s="71"/>
     </row>
     <row r="19" spans="1:12" s="72" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A19" s="66" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" s="67" t="s">
-        <v>48</v>
-      </c>
+      <c r="A19" s="66"/>
+      <c r="B19" s="67"/>
       <c r="C19" s="74"/>
       <c r="D19" s="75"/>
       <c r="E19" s="79"/>
       <c r="F19" s="75"/>
-      <c r="G19" s="75">
-        <f>SUBTOTAL(9,G20:G20)</f>
-        <v>0</v>
-      </c>
-      <c r="H19" s="75">
-        <f>SUBTOTAL(9,H20:H20)</f>
-        <v>0</v>
-      </c>
+      <c r="G19" s="75"/>
+      <c r="H19" s="75"/>
       <c r="I19" s="76"/>
       <c r="J19" s="71"/>
       <c r="K19" s="71"/>
       <c r="L19" s="71"/>
     </row>
     <row r="20" spans="1:12" s="72" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A20" s="66" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="73" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" s="74" t="s">
-        <v>43</v>
-      </c>
+      <c r="A20" s="66"/>
+      <c r="B20" s="73"/>
+      <c r="C20" s="74"/>
       <c r="D20" s="75"/>
       <c r="E20" s="75"/>
       <c r="F20" s="75"/>
-      <c r="G20" s="75">
-        <f>F20*D20</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="75">
-        <f>F20*E20</f>
-        <v>0</v>
-      </c>
+      <c r="G20" s="75"/>
+      <c r="H20" s="75"/>
       <c r="I20" s="76"/>
-      <c r="J20" s="71" t="s">
-        <v>5</v>
-      </c>
-      <c r="K20" s="71" t="s">
-        <v>14</v>
-      </c>
-      <c r="L20" s="71" t="s">
-        <v>16</v>
-      </c>
+      <c r="J20" s="71"/>
+      <c r="K20" s="71"/>
+      <c r="L20" s="71"/>
     </row>
     <row r="21" spans="1:12" s="72" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A21" s="66" t="s">
-        <v>50</v>
-      </c>
-      <c r="B21" s="67" t="s">
-        <v>51</v>
-      </c>
+      <c r="A21" s="66"/>
+      <c r="B21" s="67"/>
       <c r="C21" s="74"/>
       <c r="D21" s="75"/>
       <c r="E21" s="75"/>
@@ -3497,22 +3165,22 @@
     </row>
     <row r="22" spans="1:12" s="58" customFormat="1" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A22" s="70" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="B22" s="67" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C22" s="80"/>
       <c r="D22" s="69"/>
       <c r="E22" s="69"/>
       <c r="F22" s="69"/>
       <c r="G22" s="69">
-        <f>SUBTOTAL(9,G23:G93)</f>
-        <v>6703944.7016552296</v>
+        <f>SUBTOTAL(9,G23:G85)</f>
+        <v>0</v>
       </c>
       <c r="H22" s="69">
-        <f>SUBTOTAL(9,H23:H93)</f>
-        <v>6963516.8190324334</v>
+        <f>SUBTOTAL(9,H23:H85)</f>
+        <v>0</v>
       </c>
       <c r="I22" s="69"/>
       <c r="J22" s="57"/>
@@ -3524,7 +3192,7 @@
         <v>4</v>
       </c>
       <c r="B23" s="67" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="C23" s="68"/>
       <c r="D23" s="69"/>
@@ -3532,11 +3200,11 @@
       <c r="F23" s="69"/>
       <c r="G23" s="69">
         <f>SUBTOTAL(9,G24:G44)</f>
-        <v>1128228.3516552297</v>
+        <v>0</v>
       </c>
       <c r="H23" s="69">
         <f>SUBTOTAL(9,H24:H44)</f>
-        <v>653733.02703832497</v>
+        <v>0</v>
       </c>
       <c r="I23" s="69"/>
       <c r="J23" s="57"/>
@@ -3545,10 +3213,10 @@
     </row>
     <row r="24" spans="1:12" s="58" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="A24" s="66" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B24" s="64" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="C24" s="80"/>
       <c r="D24" s="69"/>
@@ -3556,11 +3224,11 @@
       <c r="F24" s="69"/>
       <c r="G24" s="69">
         <f>SUBTOTAL(9,G25:G31)</f>
-        <v>1128228.3516552297</v>
+        <v>0</v>
       </c>
       <c r="H24" s="69">
         <f>SUBTOTAL(9,H25:H31)</f>
-        <v>653733.02703832497</v>
+        <v>0</v>
       </c>
       <c r="I24" s="69"/>
       <c r="J24" s="57"/>
@@ -3568,259 +3236,109 @@
       <c r="L24" s="57"/>
     </row>
     <row r="25" spans="1:12" s="48" customFormat="1" ht="27.95" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.25">
-      <c r="A25" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="B25" s="63" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" s="74" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" s="81">
-        <v>11</v>
-      </c>
+      <c r="A25" s="77"/>
+      <c r="B25" s="63"/>
+      <c r="C25" s="74"/>
+      <c r="D25" s="81"/>
       <c r="E25" s="81"/>
-      <c r="F25" s="75">
-        <v>15065.824999999999</v>
-      </c>
-      <c r="G25" s="75">
-        <f t="shared" ref="G25:G31" si="0">F25*D25</f>
-        <v>165724.07499999998</v>
-      </c>
-      <c r="H25" s="75">
-        <f t="shared" ref="H25:H31" si="1">F25*E25</f>
-        <v>0</v>
-      </c>
+      <c r="F25" s="75"/>
+      <c r="G25" s="75"/>
+      <c r="H25" s="75"/>
       <c r="I25" s="76"/>
-      <c r="J25" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K25" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="L25" s="38" t="s">
-        <v>16</v>
-      </c>
+      <c r="J25" s="38"/>
+      <c r="K25" s="38"/>
+      <c r="L25" s="38"/>
     </row>
     <row r="26" spans="1:12" s="48" customFormat="1" ht="42" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.25">
-      <c r="A26" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="B26" s="63" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" s="74" t="s">
-        <v>39</v>
-      </c>
+      <c r="A26" s="77"/>
+      <c r="B26" s="63"/>
+      <c r="C26" s="74"/>
       <c r="D26" s="75"/>
-      <c r="E26" s="75">
-        <v>3</v>
-      </c>
-      <c r="F26" s="75">
-        <v>18983.05</v>
-      </c>
-      <c r="G26" s="75">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H26" s="75">
-        <f t="shared" si="1"/>
-        <v>56949.149999999994</v>
-      </c>
+      <c r="E26" s="75"/>
+      <c r="F26" s="75"/>
+      <c r="G26" s="75"/>
+      <c r="H26" s="75"/>
       <c r="I26" s="76"/>
-      <c r="J26" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K26" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="L26" s="38" t="s">
-        <v>16</v>
-      </c>
+      <c r="J26" s="38"/>
+      <c r="K26" s="38"/>
+      <c r="L26" s="38"/>
     </row>
     <row r="27" spans="1:12" s="48" customFormat="1" ht="27.95" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.25">
-      <c r="A27" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="B27" s="63" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27" s="74" t="s">
-        <v>39</v>
-      </c>
-      <c r="D27" s="75">
-        <v>3</v>
-      </c>
+      <c r="A27" s="77"/>
+      <c r="B27" s="63"/>
+      <c r="C27" s="74"/>
+      <c r="D27" s="75"/>
       <c r="E27" s="75"/>
-      <c r="F27" s="75">
-        <v>12944.888398821598</v>
-      </c>
-      <c r="G27" s="75">
-        <f t="shared" si="0"/>
-        <v>38834.665196464797</v>
-      </c>
-      <c r="H27" s="75">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F27" s="75"/>
+      <c r="G27" s="75"/>
+      <c r="H27" s="75"/>
       <c r="I27" s="76"/>
-      <c r="J27" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K27" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="L27" s="38" t="s">
-        <v>16</v>
-      </c>
+      <c r="J27" s="38"/>
+      <c r="K27" s="38"/>
+      <c r="L27" s="38"/>
     </row>
     <row r="28" spans="1:12" s="48" customFormat="1" ht="27.95" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.25">
-      <c r="A28" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" s="73" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="D28" s="75">
-        <v>46</v>
-      </c>
-      <c r="E28" s="75">
-        <v>30</v>
-      </c>
-      <c r="F28" s="75">
-        <v>18886.295901277499</v>
-      </c>
-      <c r="G28" s="75">
-        <f t="shared" si="0"/>
-        <v>868769.61145876499</v>
-      </c>
-      <c r="H28" s="75">
-        <f t="shared" si="1"/>
-        <v>566588.87703832495</v>
-      </c>
+      <c r="A28" s="77"/>
+      <c r="B28" s="73"/>
+      <c r="C28" s="74"/>
+      <c r="D28" s="75"/>
+      <c r="E28" s="75"/>
+      <c r="F28" s="75"/>
+      <c r="G28" s="75"/>
+      <c r="H28" s="75"/>
       <c r="I28" s="76"/>
-      <c r="J28" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K28" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="L28" s="38" t="s">
-        <v>16</v>
-      </c>
+      <c r="J28" s="38"/>
+      <c r="K28" s="38"/>
+      <c r="L28" s="38"/>
     </row>
     <row r="29" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.25">
-      <c r="A29" s="82" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29" s="63" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" s="75">
-        <v>180</v>
-      </c>
-      <c r="E29" s="75">
-        <v>99</v>
-      </c>
-      <c r="F29" s="83">
-        <v>305</v>
-      </c>
-      <c r="G29" s="75">
-        <f t="shared" si="0"/>
-        <v>54900</v>
-      </c>
-      <c r="H29" s="75">
-        <f t="shared" si="1"/>
-        <v>30195</v>
-      </c>
+      <c r="A29" s="82"/>
+      <c r="B29" s="63"/>
+      <c r="C29" s="74"/>
+      <c r="D29" s="75"/>
+      <c r="E29" s="75"/>
+      <c r="F29" s="83"/>
+      <c r="G29" s="75"/>
+      <c r="H29" s="75"/>
       <c r="I29" s="76"/>
-      <c r="J29" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K29" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="L29" s="38" t="s">
-        <v>16</v>
-      </c>
+      <c r="J29" s="38"/>
+      <c r="K29" s="38"/>
+      <c r="L29" s="38"/>
     </row>
     <row r="30" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.25">
-      <c r="A30" s="82" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" s="63" t="s">
-        <v>60</v>
-      </c>
-      <c r="C30" s="74" t="s">
-        <v>43</v>
-      </c>
+      <c r="A30" s="82"/>
+      <c r="B30" s="63"/>
+      <c r="C30" s="74"/>
       <c r="D30" s="75"/>
       <c r="E30" s="75"/>
       <c r="F30" s="83"/>
-      <c r="G30" s="75">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H30" s="75">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="G30" s="75"/>
+      <c r="H30" s="75"/>
       <c r="I30" s="76"/>
-      <c r="J30" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K30" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="L30" s="38" t="s">
-        <v>16</v>
-      </c>
+      <c r="J30" s="38"/>
+      <c r="K30" s="38"/>
+      <c r="L30" s="38"/>
     </row>
     <row r="31" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.25">
-      <c r="A31" s="82" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="63" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31" s="74" t="s">
-        <v>43</v>
-      </c>
+      <c r="A31" s="82"/>
+      <c r="B31" s="63"/>
+      <c r="C31" s="74"/>
       <c r="D31" s="75"/>
       <c r="E31" s="75"/>
       <c r="F31" s="83"/>
-      <c r="G31" s="75">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H31" s="75">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="G31" s="75"/>
+      <c r="H31" s="75"/>
       <c r="I31" s="76"/>
-      <c r="J31" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K31" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="L31" s="38" t="s">
-        <v>16</v>
-      </c>
+      <c r="J31" s="38"/>
+      <c r="K31" s="38"/>
+      <c r="L31" s="38"/>
     </row>
     <row r="32" spans="1:12" s="58" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="A32" s="66" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="B32" s="64" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="C32" s="80"/>
       <c r="D32" s="69"/>
@@ -3840,203 +3358,95 @@
       <c r="L32" s="57"/>
     </row>
     <row r="33" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.25">
-      <c r="A33" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="B33" s="63" t="s">
-        <v>63</v>
-      </c>
-      <c r="C33" s="74" t="s">
-        <v>39</v>
-      </c>
+      <c r="A33" s="77"/>
+      <c r="B33" s="63"/>
+      <c r="C33" s="74"/>
       <c r="D33" s="81"/>
       <c r="E33" s="81"/>
       <c r="F33" s="75"/>
-      <c r="G33" s="75">
-        <f t="shared" ref="G33:G38" si="2">F33*D33</f>
-        <v>0</v>
-      </c>
-      <c r="H33" s="75">
-        <f t="shared" ref="H33:H38" si="3">F33*E33</f>
-        <v>0</v>
-      </c>
+      <c r="G33" s="75"/>
+      <c r="H33" s="75"/>
       <c r="I33" s="76"/>
-      <c r="J33" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K33" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="L33" s="38" t="s">
-        <v>16</v>
-      </c>
+      <c r="J33" s="38"/>
+      <c r="K33" s="38"/>
+      <c r="L33" s="38"/>
     </row>
     <row r="34" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.25">
-      <c r="A34" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34" s="63" t="s">
-        <v>64</v>
-      </c>
-      <c r="C34" s="74" t="s">
-        <v>39</v>
-      </c>
+      <c r="A34" s="77"/>
+      <c r="B34" s="63"/>
+      <c r="C34" s="74"/>
       <c r="D34" s="75"/>
       <c r="E34" s="75"/>
       <c r="F34" s="75"/>
-      <c r="G34" s="75">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H34" s="75">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="G34" s="75"/>
+      <c r="H34" s="75"/>
       <c r="I34" s="76"/>
-      <c r="J34" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K34" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="L34" s="38" t="s">
-        <v>16</v>
-      </c>
+      <c r="J34" s="38"/>
+      <c r="K34" s="38"/>
+      <c r="L34" s="38"/>
     </row>
     <row r="35" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.25">
-      <c r="A35" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="B35" s="73" t="s">
-        <v>65</v>
-      </c>
-      <c r="C35" s="74" t="s">
-        <v>43</v>
-      </c>
+      <c r="A35" s="77"/>
+      <c r="B35" s="73"/>
+      <c r="C35" s="74"/>
       <c r="D35" s="75"/>
       <c r="E35" s="75"/>
       <c r="F35" s="75"/>
-      <c r="G35" s="75">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H35" s="75">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="G35" s="75"/>
+      <c r="H35" s="75"/>
       <c r="I35" s="76"/>
-      <c r="J35" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K35" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="L35" s="38" t="s">
-        <v>16</v>
-      </c>
+      <c r="J35" s="38"/>
+      <c r="K35" s="38"/>
+      <c r="L35" s="38"/>
     </row>
     <row r="36" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.25">
-      <c r="A36" s="82" t="s">
-        <v>6</v>
-      </c>
-      <c r="B36" s="63" t="s">
-        <v>66</v>
-      </c>
-      <c r="C36" s="74" t="s">
-        <v>43</v>
-      </c>
+      <c r="A36" s="82"/>
+      <c r="B36" s="63"/>
+      <c r="C36" s="74"/>
       <c r="D36" s="75"/>
       <c r="E36" s="75"/>
       <c r="F36" s="83"/>
-      <c r="G36" s="75">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H36" s="75">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="G36" s="75"/>
+      <c r="H36" s="75"/>
       <c r="I36" s="76"/>
-      <c r="J36" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K36" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="L36" s="38" t="s">
-        <v>16</v>
-      </c>
+      <c r="J36" s="38"/>
+      <c r="K36" s="38"/>
+      <c r="L36" s="38"/>
     </row>
     <row r="37" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.25">
-      <c r="A37" s="82" t="s">
-        <v>6</v>
-      </c>
-      <c r="B37" s="63" t="s">
-        <v>60</v>
-      </c>
-      <c r="C37" s="74" t="s">
-        <v>43</v>
-      </c>
+      <c r="A37" s="82"/>
+      <c r="B37" s="63"/>
+      <c r="C37" s="74"/>
       <c r="D37" s="75"/>
       <c r="E37" s="75"/>
       <c r="F37" s="83"/>
-      <c r="G37" s="75">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H37" s="75">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="G37" s="75"/>
+      <c r="H37" s="75"/>
       <c r="I37" s="76"/>
-      <c r="J37" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K37" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="L37" s="38" t="s">
-        <v>16</v>
-      </c>
+      <c r="J37" s="38"/>
+      <c r="K37" s="38"/>
+      <c r="L37" s="38"/>
     </row>
     <row r="38" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.25">
-      <c r="A38" s="82" t="s">
-        <v>6</v>
-      </c>
-      <c r="B38" s="63" t="s">
-        <v>61</v>
-      </c>
-      <c r="C38" s="74" t="s">
-        <v>43</v>
-      </c>
+      <c r="A38" s="82"/>
+      <c r="B38" s="63"/>
+      <c r="C38" s="74"/>
       <c r="D38" s="75"/>
       <c r="E38" s="75"/>
       <c r="F38" s="83"/>
-      <c r="G38" s="75">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H38" s="75">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="G38" s="75"/>
+      <c r="H38" s="75"/>
       <c r="I38" s="76"/>
-      <c r="J38" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K38" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="L38" s="38" t="s">
-        <v>16</v>
-      </c>
+      <c r="J38" s="38"/>
+      <c r="K38" s="38"/>
+      <c r="L38" s="38"/>
     </row>
     <row r="39" spans="1:12" s="58" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="A39" s="66" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B39" s="64" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="C39" s="80"/>
       <c r="D39" s="69"/>
@@ -4056,183 +3466,93 @@
       <c r="L39" s="57"/>
     </row>
     <row r="40" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.25">
-      <c r="A40" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="B40" s="63" t="s">
-        <v>68</v>
-      </c>
-      <c r="C40" s="74" t="s">
-        <v>39</v>
-      </c>
+      <c r="A40" s="77"/>
+      <c r="B40" s="63"/>
+      <c r="C40" s="74"/>
       <c r="D40" s="81"/>
       <c r="E40" s="81"/>
       <c r="F40" s="75"/>
-      <c r="G40" s="75">
-        <f>F40*D40</f>
-        <v>0</v>
-      </c>
-      <c r="H40" s="75">
-        <f>F40*E40</f>
-        <v>0</v>
-      </c>
+      <c r="G40" s="75"/>
+      <c r="H40" s="75"/>
       <c r="I40" s="76"/>
-      <c r="J40" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K40" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="L40" s="38" t="s">
-        <v>16</v>
-      </c>
+      <c r="J40" s="38"/>
+      <c r="K40" s="38"/>
+      <c r="L40" s="38"/>
     </row>
     <row r="41" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.25">
-      <c r="A41" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="B41" s="63" t="s">
-        <v>69</v>
-      </c>
-      <c r="C41" s="74" t="s">
-        <v>39</v>
-      </c>
+      <c r="A41" s="77"/>
+      <c r="B41" s="63"/>
+      <c r="C41" s="74"/>
       <c r="D41" s="75"/>
       <c r="E41" s="75"/>
       <c r="F41" s="75"/>
-      <c r="G41" s="75">
-        <f>F41*D41</f>
-        <v>0</v>
-      </c>
-      <c r="H41" s="75">
-        <f>F41*E41</f>
-        <v>0</v>
-      </c>
+      <c r="G41" s="75"/>
+      <c r="H41" s="75"/>
       <c r="I41" s="76"/>
-      <c r="J41" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K41" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="L41" s="38" t="s">
-        <v>16</v>
-      </c>
+      <c r="J41" s="38"/>
+      <c r="K41" s="38"/>
+      <c r="L41" s="38"/>
     </row>
     <row r="42" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.25">
-      <c r="A42" s="82" t="s">
-        <v>6</v>
-      </c>
-      <c r="B42" s="63" t="s">
-        <v>66</v>
-      </c>
-      <c r="C42" s="74" t="s">
-        <v>43</v>
-      </c>
+      <c r="A42" s="82"/>
+      <c r="B42" s="63"/>
+      <c r="C42" s="74"/>
       <c r="D42" s="75"/>
       <c r="E42" s="75"/>
       <c r="F42" s="83"/>
-      <c r="G42" s="75">
-        <f>F42*D42</f>
-        <v>0</v>
-      </c>
-      <c r="H42" s="75">
-        <f>F42*E42</f>
-        <v>0</v>
-      </c>
+      <c r="G42" s="75"/>
+      <c r="H42" s="75"/>
       <c r="I42" s="76"/>
-      <c r="J42" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K42" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="L42" s="38" t="s">
-        <v>16</v>
-      </c>
+      <c r="J42" s="38"/>
+      <c r="K42" s="38"/>
+      <c r="L42" s="38"/>
     </row>
     <row r="43" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.25">
-      <c r="A43" s="82" t="s">
-        <v>6</v>
-      </c>
-      <c r="B43" s="63" t="s">
-        <v>60</v>
-      </c>
-      <c r="C43" s="74" t="s">
-        <v>43</v>
-      </c>
+      <c r="A43" s="82"/>
+      <c r="B43" s="63"/>
+      <c r="C43" s="74"/>
       <c r="D43" s="75"/>
       <c r="E43" s="75"/>
       <c r="F43" s="83"/>
-      <c r="G43" s="75">
-        <f>F43*D43</f>
-        <v>0</v>
-      </c>
-      <c r="H43" s="75">
-        <f>F43*E43</f>
-        <v>0</v>
-      </c>
+      <c r="G43" s="75"/>
+      <c r="H43" s="75"/>
       <c r="I43" s="76"/>
-      <c r="J43" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K43" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="L43" s="38" t="s">
-        <v>16</v>
-      </c>
+      <c r="J43" s="38"/>
+      <c r="K43" s="38"/>
+      <c r="L43" s="38"/>
     </row>
     <row r="44" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.25">
-      <c r="A44" s="82" t="s">
-        <v>6</v>
-      </c>
-      <c r="B44" s="63" t="s">
-        <v>61</v>
-      </c>
-      <c r="C44" s="74" t="s">
-        <v>43</v>
-      </c>
+      <c r="A44" s="82"/>
+      <c r="B44" s="63"/>
+      <c r="C44" s="74"/>
       <c r="D44" s="75"/>
       <c r="E44" s="75"/>
       <c r="F44" s="83"/>
-      <c r="G44" s="75">
-        <f>F44*D44</f>
-        <v>0</v>
-      </c>
-      <c r="H44" s="75">
-        <f>F44*E44</f>
-        <v>0</v>
-      </c>
+      <c r="G44" s="75"/>
+      <c r="H44" s="75"/>
       <c r="I44" s="76"/>
-      <c r="J44" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K44" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="L44" s="38" t="s">
-        <v>16</v>
-      </c>
+      <c r="J44" s="38"/>
+      <c r="K44" s="38"/>
+      <c r="L44" s="38"/>
     </row>
     <row r="45" spans="1:12" s="58" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A45" s="70" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B45" s="67" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="C45" s="68"/>
       <c r="D45" s="69"/>
       <c r="E45" s="69"/>
       <c r="F45" s="69"/>
       <c r="G45" s="69">
-        <f>SUBTOTAL(9,G46:G73)</f>
-        <v>5040295.3499999996</v>
+        <f>SUBTOTAL(9,G46:G65)</f>
+        <v>0</v>
       </c>
       <c r="H45" s="69">
-        <f>SUBTOTAL(9,H46:H73)</f>
-        <v>5608483.7919941079</v>
+        <f>SUBTOTAL(9,H46:H65)</f>
+        <v>0</v>
       </c>
       <c r="I45" s="69"/>
       <c r="J45" s="57"/>
@@ -4241,1591 +3561,624 @@
     </row>
     <row r="46" spans="1:12" s="58" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="A46" s="66" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B46" s="64" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="C46" s="80"/>
       <c r="D46" s="69"/>
       <c r="E46" s="69"/>
       <c r="F46" s="69"/>
       <c r="G46" s="69">
-        <f>SUBTOTAL(9,G47:G59)</f>
-        <v>5040295.3499999996</v>
+        <f>SUBTOTAL(9,G47:G51)</f>
+        <v>0</v>
       </c>
       <c r="H46" s="69">
-        <f>SUBTOTAL(9,H47:H59)</f>
-        <v>5608483.7919941079</v>
+        <f>SUBTOTAL(9,H47:H51)</f>
+        <v>0</v>
       </c>
       <c r="I46" s="69"/>
       <c r="J46" s="57"/>
       <c r="K46" s="57"/>
       <c r="L46" s="57"/>
     </row>
-    <row r="47" spans="1:12" s="48" customFormat="1" ht="27.95" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A47" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" s="63" t="s">
-        <v>55</v>
-      </c>
-      <c r="C47" s="78" t="s">
-        <v>39</v>
-      </c>
-      <c r="D47" s="90">
-        <v>38</v>
-      </c>
-      <c r="E47" s="90"/>
-      <c r="F47" s="75">
-        <v>15065.824999999999</v>
-      </c>
-      <c r="G47" s="75">
-        <f t="shared" ref="G47:G59" si="4">F47*D47</f>
-        <v>572501.35</v>
-      </c>
-      <c r="H47" s="75">
-        <f t="shared" ref="H47:H59" si="5">F47*E47</f>
+    <row r="47" spans="1:12" s="48" customFormat="1" ht="42" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
+      <c r="A47" s="82"/>
+      <c r="B47" s="90"/>
+      <c r="C47" s="78"/>
+      <c r="D47" s="75"/>
+      <c r="F47" s="83"/>
+      <c r="G47" s="75"/>
+      <c r="H47" s="75"/>
+      <c r="I47" s="76"/>
+      <c r="J47" s="38"/>
+      <c r="K47" s="38"/>
+      <c r="L47" s="38"/>
+    </row>
+    <row r="48" spans="1:12" s="48" customFormat="1" ht="42" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
+      <c r="A48" s="82"/>
+      <c r="B48" s="88"/>
+      <c r="C48" s="78"/>
+      <c r="D48" s="75"/>
+      <c r="F48" s="83"/>
+      <c r="G48" s="75"/>
+      <c r="H48" s="75"/>
+      <c r="I48" s="76"/>
+      <c r="J48" s="38"/>
+      <c r="K48" s="38"/>
+      <c r="L48" s="38"/>
+    </row>
+    <row r="49" spans="1:12" s="48" customFormat="1" ht="27.95" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
+      <c r="A49" s="82"/>
+      <c r="B49" s="91"/>
+      <c r="C49" s="89"/>
+      <c r="D49" s="75"/>
+      <c r="E49" s="75"/>
+      <c r="F49" s="83"/>
+      <c r="G49" s="75"/>
+      <c r="H49" s="75"/>
+      <c r="I49" s="76"/>
+      <c r="J49" s="38"/>
+      <c r="K49" s="38"/>
+      <c r="L49" s="38"/>
+    </row>
+    <row r="50" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
+      <c r="A50" s="82"/>
+      <c r="B50" s="63"/>
+      <c r="C50" s="78"/>
+      <c r="D50" s="75"/>
+      <c r="E50" s="75"/>
+      <c r="F50" s="83"/>
+      <c r="G50" s="75"/>
+      <c r="H50" s="75"/>
+      <c r="I50" s="76"/>
+      <c r="J50" s="38"/>
+      <c r="K50" s="38"/>
+      <c r="L50" s="38"/>
+    </row>
+    <row r="51" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
+      <c r="A51" s="82"/>
+      <c r="B51" s="63"/>
+      <c r="C51" s="78"/>
+      <c r="D51" s="75"/>
+      <c r="E51" s="75"/>
+      <c r="F51" s="83"/>
+      <c r="G51" s="75"/>
+      <c r="H51" s="75"/>
+      <c r="I51" s="76"/>
+      <c r="J51" s="38"/>
+      <c r="K51" s="38"/>
+      <c r="L51" s="38"/>
+    </row>
+    <row r="52" spans="1:12" s="58" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
+      <c r="A52" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="B52" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52" s="80"/>
+      <c r="D52" s="69"/>
+      <c r="E52" s="69"/>
+      <c r="F52" s="69"/>
+      <c r="G52" s="69">
+        <f>SUBTOTAL(9,G53:G58)</f>
         <v>0</v>
       </c>
-      <c r="I47" s="76"/>
-      <c r="J47" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K47" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L47" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" s="48" customFormat="1" ht="42" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A48" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="B48" s="63" t="s">
-        <v>56</v>
-      </c>
-      <c r="C48" s="78" t="s">
-        <v>39</v>
-      </c>
-      <c r="D48" s="75"/>
-      <c r="E48" s="75">
-        <v>35</v>
-      </c>
-      <c r="F48" s="75">
-        <v>18983.05</v>
-      </c>
-      <c r="G48" s="75">
-        <f t="shared" si="4"/>
+      <c r="H52" s="69">
+        <f>SUBTOTAL(9,H53:H58)</f>
         <v>0</v>
       </c>
-      <c r="H48" s="75">
-        <f t="shared" si="5"/>
-        <v>664406.75</v>
-      </c>
-      <c r="I48" s="76"/>
-      <c r="J48" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K48" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L48" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" s="48" customFormat="1" ht="27.95" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A49" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="B49" s="63" t="s">
-        <v>71</v>
-      </c>
-      <c r="C49" s="78" t="s">
-        <v>39</v>
-      </c>
-      <c r="D49" s="75">
-        <v>6</v>
-      </c>
-      <c r="E49" s="75">
-        <v>12</v>
-      </c>
-      <c r="F49" s="75">
-        <v>16686.800000000003</v>
-      </c>
-      <c r="G49" s="75">
-        <f t="shared" si="4"/>
-        <v>100120.80000000002</v>
-      </c>
-      <c r="H49" s="75">
-        <f t="shared" si="5"/>
-        <v>200241.60000000003</v>
-      </c>
-      <c r="I49" s="76"/>
-      <c r="J49" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K49" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L49" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" s="48" customFormat="1" ht="27.95" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A50" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="B50" s="63" t="s">
-        <v>72</v>
-      </c>
-      <c r="C50" s="78" t="s">
-        <v>39</v>
-      </c>
-      <c r="D50" s="75">
-        <v>181</v>
-      </c>
-      <c r="E50" s="75">
-        <v>146</v>
-      </c>
-      <c r="F50" s="75">
-        <v>11686.800000000001</v>
-      </c>
-      <c r="G50" s="75">
-        <f t="shared" si="4"/>
-        <v>2115310.8000000003</v>
-      </c>
-      <c r="H50" s="75">
-        <f t="shared" si="5"/>
-        <v>1706272.8</v>
-      </c>
-      <c r="I50" s="76"/>
-      <c r="J50" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K50" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L50" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" s="48" customFormat="1" ht="27.95" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A51" s="82" t="s">
-        <v>6</v>
-      </c>
-      <c r="B51" s="63" t="s">
-        <v>73</v>
-      </c>
-      <c r="C51" s="78" t="s">
-        <v>39</v>
-      </c>
-      <c r="D51" s="75">
-        <v>20</v>
-      </c>
-      <c r="E51" s="75"/>
-      <c r="F51" s="83">
-        <v>10000</v>
-      </c>
-      <c r="G51" s="75">
-        <f t="shared" si="4"/>
-        <v>200000</v>
-      </c>
-      <c r="H51" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="I51" s="76"/>
-      <c r="J51" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K51" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L51" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" s="48" customFormat="1" ht="42" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A52" s="82" t="s">
-        <v>6</v>
-      </c>
-      <c r="B52" s="88" t="s">
-        <v>36</v>
-      </c>
-      <c r="C52" s="78" t="s">
-        <v>39</v>
-      </c>
-      <c r="D52" s="75">
-        <v>22</v>
-      </c>
-      <c r="E52" s="75">
-        <v>36</v>
-      </c>
-      <c r="F52" s="83">
-        <v>24000</v>
-      </c>
-      <c r="G52" s="75">
-        <f t="shared" si="4"/>
-        <v>528000</v>
-      </c>
-      <c r="H52" s="75">
-        <f t="shared" si="5"/>
-        <v>864000</v>
-      </c>
-      <c r="I52" s="76"/>
-      <c r="J52" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K52" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L52" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" s="48" customFormat="1" ht="27.95" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A53" s="82" t="s">
-        <v>6</v>
-      </c>
-      <c r="B53" s="91" t="s">
-        <v>57</v>
-      </c>
-      <c r="C53" s="78" t="s">
-        <v>39</v>
-      </c>
-      <c r="D53" s="75"/>
-      <c r="E53" s="75">
-        <v>5</v>
-      </c>
-      <c r="F53" s="83">
-        <v>12944.888398821598</v>
-      </c>
-      <c r="G53" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H53" s="75">
-        <f t="shared" si="5"/>
-        <v>64724.44199410799</v>
-      </c>
+      <c r="I52" s="69"/>
+      <c r="J52" s="57"/>
+      <c r="K52" s="57"/>
+      <c r="L52" s="57"/>
+    </row>
+    <row r="53" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
+      <c r="A53" s="77"/>
+      <c r="B53" s="63"/>
+      <c r="C53" s="74"/>
+      <c r="D53" s="81"/>
+      <c r="E53" s="81"/>
+      <c r="F53" s="75"/>
+      <c r="G53" s="75"/>
+      <c r="H53" s="75"/>
       <c r="I53" s="76"/>
-      <c r="J53" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K53" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L53" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" s="48" customFormat="1" ht="42" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A54" s="82" t="s">
-        <v>6</v>
-      </c>
-      <c r="B54" s="91" t="s">
-        <v>74</v>
-      </c>
-      <c r="C54" s="78" t="s">
-        <v>39</v>
-      </c>
+      <c r="J53" s="38"/>
+      <c r="K53" s="38"/>
+      <c r="L53" s="38"/>
+    </row>
+    <row r="54" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
+      <c r="A54" s="77"/>
+      <c r="B54" s="63"/>
+      <c r="C54" s="74"/>
       <c r="D54" s="75"/>
-      <c r="E54" s="75">
-        <v>10</v>
-      </c>
-      <c r="F54" s="83">
-        <v>16686.800000000003</v>
-      </c>
-      <c r="G54" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H54" s="75">
-        <f t="shared" si="5"/>
-        <v>166868.00000000003</v>
-      </c>
+      <c r="E54" s="75"/>
+      <c r="F54" s="75"/>
+      <c r="G54" s="75"/>
+      <c r="H54" s="75"/>
       <c r="I54" s="76"/>
-      <c r="J54" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K54" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L54" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" s="48" customFormat="1" ht="42" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A55" s="82" t="s">
-        <v>6</v>
-      </c>
-      <c r="B55" s="91" t="s">
-        <v>75</v>
-      </c>
-      <c r="C55" s="78" t="s">
-        <v>39</v>
-      </c>
-      <c r="D55" s="75">
-        <v>61</v>
-      </c>
-      <c r="E55" s="48">
-        <v>139</v>
-      </c>
-      <c r="F55" s="83">
-        <v>11686.800000000001</v>
-      </c>
-      <c r="G55" s="75">
-        <f t="shared" si="4"/>
-        <v>712894.8</v>
-      </c>
-      <c r="H55" s="75">
-        <f t="shared" si="5"/>
-        <v>1624465.2000000002</v>
-      </c>
+      <c r="J54" s="38"/>
+      <c r="K54" s="38"/>
+      <c r="L54" s="38"/>
+    </row>
+    <row r="55" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
+      <c r="A55" s="77"/>
+      <c r="B55" s="73"/>
+      <c r="C55" s="74"/>
+      <c r="D55" s="75"/>
+      <c r="E55" s="75"/>
+      <c r="F55" s="75"/>
+      <c r="G55" s="75"/>
+      <c r="H55" s="75"/>
       <c r="I55" s="76"/>
-      <c r="J55" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K55" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L55" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" s="48" customFormat="1" ht="42" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A56" s="82" t="s">
-        <v>6</v>
-      </c>
-      <c r="B56" s="88" t="s">
-        <v>76</v>
-      </c>
-      <c r="C56" s="78" t="s">
-        <v>39</v>
-      </c>
-      <c r="D56" s="75">
-        <v>18</v>
-      </c>
-      <c r="F56" s="83">
-        <v>24000</v>
-      </c>
-      <c r="G56" s="75">
-        <f t="shared" si="4"/>
-        <v>432000</v>
-      </c>
-      <c r="H56" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="J55" s="38"/>
+      <c r="K55" s="38"/>
+      <c r="L55" s="38"/>
+    </row>
+    <row r="56" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
+      <c r="A56" s="77"/>
+      <c r="B56" s="63"/>
+      <c r="C56" s="74"/>
+      <c r="D56" s="75"/>
+      <c r="E56" s="75"/>
+      <c r="F56" s="75"/>
+      <c r="G56" s="75"/>
+      <c r="H56" s="75"/>
       <c r="I56" s="76"/>
-      <c r="J56" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K56" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L56" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" s="48" customFormat="1" ht="27.95" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A57" s="82" t="s">
-        <v>6</v>
-      </c>
-      <c r="B57" s="92" t="s">
-        <v>77</v>
-      </c>
-      <c r="C57" s="89" t="s">
-        <v>39</v>
-      </c>
-      <c r="D57" s="75">
-        <v>32</v>
-      </c>
+      <c r="J56" s="38"/>
+      <c r="K56" s="38"/>
+      <c r="L56" s="38"/>
+    </row>
+    <row r="57" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
+      <c r="A57" s="82"/>
+      <c r="B57" s="63"/>
+      <c r="C57" s="74"/>
+      <c r="D57" s="75"/>
       <c r="E57" s="75"/>
-      <c r="F57" s="83">
-        <v>11686.800000000001</v>
-      </c>
-      <c r="G57" s="75">
-        <f t="shared" si="4"/>
-        <v>373977.60000000003</v>
-      </c>
-      <c r="H57" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="F57" s="83"/>
+      <c r="G57" s="75"/>
+      <c r="H57" s="75"/>
       <c r="I57" s="76"/>
-      <c r="J57" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K57" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L57" s="38" t="s">
-        <v>16</v>
-      </c>
+      <c r="J57" s="38"/>
+      <c r="K57" s="38"/>
+      <c r="L57" s="38"/>
     </row>
     <row r="58" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A58" s="82" t="s">
-        <v>6</v>
-      </c>
-      <c r="B58" s="63" t="s">
-        <v>60</v>
-      </c>
-      <c r="C58" s="78" t="s">
-        <v>78</v>
-      </c>
+      <c r="A58" s="82"/>
+      <c r="B58" s="63"/>
+      <c r="C58" s="74"/>
       <c r="D58" s="75"/>
       <c r="E58" s="75"/>
       <c r="F58" s="83"/>
-      <c r="G58" s="75">
-        <f t="shared" si="4"/>
+      <c r="G58" s="75"/>
+      <c r="H58" s="75"/>
+      <c r="I58" s="76"/>
+      <c r="J58" s="38"/>
+      <c r="K58" s="38"/>
+      <c r="L58" s="38"/>
+    </row>
+    <row r="59" spans="1:12" s="58" customFormat="1" ht="13.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
+      <c r="A59" s="66" t="s">
+        <v>28</v>
+      </c>
+      <c r="B59" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="C59" s="80"/>
+      <c r="D59" s="69"/>
+      <c r="E59" s="69"/>
+      <c r="F59" s="69"/>
+      <c r="G59" s="69">
+        <f>SUBTOTAL(9,G60:G65)</f>
         <v>0</v>
       </c>
-      <c r="H58" s="75">
-        <f t="shared" si="5"/>
+      <c r="H59" s="69">
+        <f>SUBTOTAL(9,H60:H65)</f>
         <v>0</v>
       </c>
-      <c r="I58" s="76"/>
-      <c r="J58" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K58" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L58" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A59" s="82" t="s">
-        <v>6</v>
-      </c>
-      <c r="B59" s="63" t="s">
-        <v>59</v>
-      </c>
-      <c r="C59" s="78" t="s">
-        <v>78</v>
-      </c>
-      <c r="D59" s="75">
-        <v>18</v>
-      </c>
-      <c r="E59" s="75">
-        <v>1041</v>
-      </c>
-      <c r="F59" s="83">
-        <v>305</v>
-      </c>
-      <c r="G59" s="75">
-        <f t="shared" si="4"/>
-        <v>5490</v>
-      </c>
-      <c r="H59" s="75">
-        <f t="shared" si="5"/>
-        <v>317505</v>
-      </c>
-      <c r="I59" s="76"/>
-      <c r="J59" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K59" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L59" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" s="58" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A60" s="66" t="s">
-        <v>34</v>
-      </c>
-      <c r="B60" s="64" t="s">
-        <v>62</v>
-      </c>
-      <c r="C60" s="80"/>
-      <c r="D60" s="69"/>
-      <c r="E60" s="69"/>
-      <c r="F60" s="69"/>
-      <c r="G60" s="69">
-        <f>SUBTOTAL(9,G61:G66)</f>
-        <v>0</v>
-      </c>
-      <c r="H60" s="69">
-        <f>SUBTOTAL(9,H61:H66)</f>
-        <v>0</v>
-      </c>
-      <c r="I60" s="69"/>
-      <c r="J60" s="57"/>
-      <c r="K60" s="57"/>
-      <c r="L60" s="57"/>
+      <c r="I59" s="69"/>
+      <c r="J59" s="57"/>
+      <c r="K59" s="57"/>
+      <c r="L59" s="57"/>
+    </row>
+    <row r="60" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
+      <c r="A60" s="77"/>
+      <c r="B60" s="63"/>
+      <c r="C60" s="74"/>
+      <c r="D60" s="81"/>
+      <c r="E60" s="81"/>
+      <c r="F60" s="83"/>
+      <c r="G60" s="75"/>
+      <c r="H60" s="75"/>
+      <c r="I60" s="76"/>
+      <c r="J60" s="38"/>
+      <c r="K60" s="38"/>
+      <c r="L60" s="38"/>
     </row>
     <row r="61" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A61" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="B61" s="63" t="s">
-        <v>63</v>
-      </c>
-      <c r="C61" s="74" t="s">
-        <v>39</v>
-      </c>
+      <c r="A61" s="77"/>
+      <c r="B61" s="63"/>
+      <c r="C61" s="74"/>
       <c r="D61" s="81"/>
       <c r="E61" s="81"/>
-      <c r="F61" s="75"/>
-      <c r="G61" s="75">
-        <f t="shared" ref="G61:G66" si="6">F61*D61</f>
-        <v>0</v>
-      </c>
-      <c r="H61" s="75">
-        <f t="shared" ref="H61:H66" si="7">F61*E61</f>
-        <v>0</v>
-      </c>
+      <c r="F61" s="83"/>
+      <c r="G61" s="75"/>
+      <c r="H61" s="75"/>
       <c r="I61" s="76"/>
-      <c r="J61" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K61" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L61" s="38" t="s">
-        <v>16</v>
-      </c>
+      <c r="J61" s="38"/>
+      <c r="K61" s="38"/>
+      <c r="L61" s="38"/>
     </row>
     <row r="62" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A62" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="B62" s="63" t="s">
-        <v>64</v>
-      </c>
-      <c r="C62" s="74" t="s">
-        <v>39</v>
-      </c>
+      <c r="A62" s="77"/>
+      <c r="B62" s="63"/>
+      <c r="C62" s="74"/>
       <c r="D62" s="75"/>
       <c r="E62" s="75"/>
-      <c r="F62" s="75"/>
-      <c r="G62" s="75">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H62" s="75">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
+      <c r="F62" s="83"/>
+      <c r="G62" s="75"/>
+      <c r="H62" s="75"/>
       <c r="I62" s="76"/>
-      <c r="J62" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K62" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L62" s="38" t="s">
-        <v>16</v>
-      </c>
+      <c r="J62" s="38"/>
+      <c r="K62" s="38"/>
+      <c r="L62" s="38"/>
     </row>
     <row r="63" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A63" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="B63" s="73" t="s">
-        <v>65</v>
-      </c>
-      <c r="C63" s="74" t="s">
-        <v>43</v>
-      </c>
+      <c r="A63" s="77"/>
+      <c r="B63" s="63"/>
+      <c r="C63" s="74"/>
       <c r="D63" s="75"/>
       <c r="E63" s="75"/>
-      <c r="F63" s="75"/>
-      <c r="G63" s="75">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H63" s="75">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
+      <c r="F63" s="83"/>
+      <c r="G63" s="75"/>
+      <c r="H63" s="75"/>
       <c r="I63" s="76"/>
-      <c r="J63" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K63" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L63" s="38" t="s">
-        <v>16</v>
-      </c>
+      <c r="J63" s="38"/>
+      <c r="K63" s="38"/>
+      <c r="L63" s="38"/>
     </row>
     <row r="64" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A64" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="B64" s="63" t="s">
-        <v>66</v>
-      </c>
-      <c r="C64" s="74" t="s">
-        <v>43</v>
-      </c>
+      <c r="A64" s="77"/>
+      <c r="B64" s="63"/>
+      <c r="C64" s="74"/>
       <c r="D64" s="75"/>
       <c r="E64" s="75"/>
-      <c r="F64" s="75"/>
-      <c r="G64" s="75">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H64" s="75">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
+      <c r="F64" s="83"/>
+      <c r="G64" s="75"/>
+      <c r="H64" s="75"/>
       <c r="I64" s="76"/>
-      <c r="J64" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K64" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L64" s="38" t="s">
-        <v>16</v>
-      </c>
+      <c r="J64" s="38"/>
+      <c r="K64" s="38"/>
+      <c r="L64" s="38"/>
     </row>
     <row r="65" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A65" s="82" t="s">
-        <v>6</v>
-      </c>
-      <c r="B65" s="63" t="s">
-        <v>60</v>
-      </c>
-      <c r="C65" s="74" t="s">
-        <v>43</v>
-      </c>
+      <c r="A65" s="82"/>
+      <c r="B65" s="63"/>
+      <c r="C65" s="74"/>
       <c r="D65" s="75"/>
       <c r="E65" s="75"/>
       <c r="F65" s="83"/>
-      <c r="G65" s="75">
-        <f t="shared" si="6"/>
+      <c r="G65" s="75"/>
+      <c r="H65" s="75"/>
+      <c r="I65" s="76"/>
+      <c r="J65" s="38"/>
+      <c r="K65" s="38"/>
+      <c r="L65" s="38"/>
+    </row>
+    <row r="66" spans="1:12" s="58" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A66" s="66" t="s">
+        <v>6</v>
+      </c>
+      <c r="B66" s="67" t="s">
+        <v>35</v>
+      </c>
+      <c r="C66" s="68"/>
+      <c r="D66" s="69"/>
+      <c r="E66" s="69"/>
+      <c r="F66" s="69"/>
+      <c r="G66" s="69">
+        <f>SUBTOTAL(9,G67:G68)</f>
         <v>0</v>
       </c>
-      <c r="H65" s="75">
-        <f t="shared" si="7"/>
+      <c r="H66" s="69">
+        <f>SUBTOTAL(9,H67:H68)</f>
         <v>0</v>
       </c>
-      <c r="I65" s="76"/>
-      <c r="J65" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K65" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L65" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A66" s="82" t="s">
-        <v>6</v>
-      </c>
-      <c r="B66" s="63" t="s">
-        <v>61</v>
-      </c>
-      <c r="C66" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="D66" s="75"/>
-      <c r="E66" s="75"/>
-      <c r="F66" s="83"/>
-      <c r="G66" s="75">
-        <f t="shared" si="6"/>
+      <c r="I66" s="70"/>
+      <c r="J66" s="38"/>
+      <c r="K66" s="38"/>
+      <c r="L66" s="38"/>
+    </row>
+    <row r="67" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A67" s="77"/>
+      <c r="B67" s="63"/>
+      <c r="C67" s="74"/>
+      <c r="D67" s="75"/>
+      <c r="E67" s="75"/>
+      <c r="F67" s="75"/>
+      <c r="G67" s="75"/>
+      <c r="H67" s="75"/>
+      <c r="I67" s="76"/>
+      <c r="J67" s="38"/>
+      <c r="K67" s="38"/>
+      <c r="L67" s="38"/>
+    </row>
+    <row r="68" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A68" s="77"/>
+      <c r="B68" s="63"/>
+      <c r="C68" s="74"/>
+      <c r="D68" s="75"/>
+      <c r="E68" s="75"/>
+      <c r="F68" s="75"/>
+      <c r="G68" s="75"/>
+      <c r="H68" s="75"/>
+      <c r="I68" s="76"/>
+      <c r="J68" s="38"/>
+      <c r="K68" s="38"/>
+      <c r="L68" s="38"/>
+    </row>
+    <row r="69" spans="1:12" s="58" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A69" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="B69" s="84" t="s">
+        <v>36</v>
+      </c>
+      <c r="C69" s="68"/>
+      <c r="D69" s="69"/>
+      <c r="E69" s="69"/>
+      <c r="F69" s="69"/>
+      <c r="G69" s="69">
+        <f>SUBTOTAL(9,G70:G80)</f>
         <v>0</v>
       </c>
-      <c r="H66" s="75">
-        <f t="shared" si="7"/>
+      <c r="H69" s="69">
+        <f>SUBTOTAL(9,H70:H80)</f>
         <v>0</v>
       </c>
-      <c r="I66" s="76"/>
-      <c r="J66" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K66" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L66" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" s="58" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A67" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="B67" s="64" t="s">
-        <v>67</v>
-      </c>
-      <c r="C67" s="80"/>
-      <c r="D67" s="69"/>
-      <c r="E67" s="69"/>
-      <c r="F67" s="69"/>
-      <c r="G67" s="69">
-        <f>SUBTOTAL(9,G68:G73)</f>
-        <v>0</v>
-      </c>
-      <c r="H67" s="69">
-        <f>SUBTOTAL(9,H68:H73)</f>
-        <v>0</v>
-      </c>
-      <c r="I67" s="69"/>
-      <c r="J67" s="57"/>
-      <c r="K67" s="57"/>
-      <c r="L67" s="57"/>
-    </row>
-    <row r="68" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A68" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="B68" s="63" t="s">
-        <v>79</v>
-      </c>
-      <c r="C68" s="74" t="s">
-        <v>39</v>
-      </c>
-      <c r="D68" s="81"/>
-      <c r="E68" s="81"/>
-      <c r="F68" s="83"/>
-      <c r="G68" s="75">
-        <f t="shared" ref="G68:G73" si="8">F68*D68</f>
-        <v>0</v>
-      </c>
-      <c r="H68" s="75">
-        <f t="shared" ref="H68:H73" si="9">F68*E68</f>
-        <v>0</v>
-      </c>
-      <c r="I68" s="76"/>
-      <c r="J68" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K68" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L68" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A69" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="B69" s="63" t="s">
-        <v>80</v>
-      </c>
-      <c r="C69" s="74" t="s">
-        <v>39</v>
-      </c>
-      <c r="D69" s="81"/>
-      <c r="E69" s="81"/>
-      <c r="F69" s="83"/>
-      <c r="G69" s="75">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H69" s="75">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
       <c r="I69" s="76"/>
-      <c r="J69" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K69" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L69" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A70" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="B70" s="63" t="s">
-        <v>69</v>
-      </c>
-      <c r="C70" s="74" t="s">
-        <v>39</v>
-      </c>
-      <c r="D70" s="75"/>
-      <c r="E70" s="75"/>
-      <c r="F70" s="83"/>
-      <c r="G70" s="75">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H70" s="75">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="I70" s="76"/>
-      <c r="J70" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K70" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L70" s="38" t="s">
-        <v>16</v>
-      </c>
+      <c r="J69" s="38"/>
+      <c r="K69" s="38"/>
+      <c r="L69" s="38"/>
+    </row>
+    <row r="70" spans="1:12" s="58" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
+      <c r="A70" s="66"/>
+      <c r="B70" s="67"/>
+      <c r="C70" s="68"/>
+      <c r="D70" s="69"/>
+      <c r="E70" s="69"/>
+      <c r="F70" s="69"/>
+      <c r="G70" s="69"/>
+      <c r="H70" s="69"/>
+      <c r="I70" s="70"/>
+      <c r="J70" s="57"/>
+      <c r="K70" s="57"/>
+      <c r="L70" s="57"/>
     </row>
     <row r="71" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A71" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="B71" s="63" t="s">
-        <v>66</v>
-      </c>
-      <c r="C71" s="74" t="s">
-        <v>43</v>
-      </c>
+      <c r="A71" s="66"/>
+      <c r="B71" s="73"/>
+      <c r="C71" s="74"/>
       <c r="D71" s="75"/>
       <c r="E71" s="75"/>
-      <c r="F71" s="83"/>
-      <c r="G71" s="75">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H71" s="75">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="F71" s="75"/>
+      <c r="G71" s="75"/>
+      <c r="H71" s="75"/>
       <c r="I71" s="76"/>
-      <c r="J71" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K71" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L71" s="38" t="s">
-        <v>16</v>
-      </c>
+      <c r="J71" s="38"/>
+      <c r="K71" s="38"/>
+      <c r="L71" s="38"/>
     </row>
     <row r="72" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A72" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="B72" s="63" t="s">
-        <v>60</v>
-      </c>
-      <c r="C72" s="74" t="s">
-        <v>43</v>
-      </c>
+      <c r="A72" s="66"/>
+      <c r="B72" s="73"/>
+      <c r="C72" s="74"/>
       <c r="D72" s="75"/>
       <c r="E72" s="75"/>
-      <c r="F72" s="83"/>
-      <c r="G72" s="75">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H72" s="75">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="F72" s="75"/>
+      <c r="G72" s="75"/>
+      <c r="H72" s="75"/>
       <c r="I72" s="76"/>
-      <c r="J72" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K72" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L72" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A73" s="82" t="s">
-        <v>6</v>
-      </c>
-      <c r="B73" s="63" t="s">
-        <v>61</v>
-      </c>
-      <c r="C73" s="74" t="s">
-        <v>43</v>
-      </c>
+      <c r="J72" s="38"/>
+      <c r="K72" s="38"/>
+      <c r="L72" s="38"/>
+    </row>
+    <row r="73" spans="1:12" s="48" customFormat="1" ht="13.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A73" s="66"/>
+      <c r="B73" s="73"/>
+      <c r="C73" s="74"/>
       <c r="D73" s="75"/>
       <c r="E73" s="75"/>
-      <c r="F73" s="83"/>
-      <c r="G73" s="75">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H73" s="75">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="F73" s="75"/>
+      <c r="G73" s="75"/>
+      <c r="H73" s="75"/>
       <c r="I73" s="76"/>
-      <c r="J73" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K73" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L73" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" s="58" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A74" s="66" t="s">
-        <v>7</v>
-      </c>
-      <c r="B74" s="67" t="s">
-        <v>81</v>
-      </c>
-      <c r="C74" s="68"/>
-      <c r="D74" s="69"/>
-      <c r="E74" s="69"/>
-      <c r="F74" s="69"/>
-      <c r="G74" s="69">
-        <f>SUBTOTAL(9,G75:G76)</f>
-        <v>0</v>
-      </c>
-      <c r="H74" s="69">
-        <f>SUBTOTAL(9,H75:H76)</f>
-        <v>0</v>
-      </c>
-      <c r="I74" s="70"/>
+      <c r="J73" s="38"/>
+      <c r="K73" s="38"/>
+      <c r="L73" s="38"/>
+    </row>
+    <row r="74" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A74" s="66"/>
+      <c r="B74" s="73"/>
+      <c r="C74" s="74"/>
+      <c r="D74" s="75"/>
+      <c r="E74" s="75"/>
+      <c r="F74" s="75"/>
+      <c r="G74" s="75"/>
+      <c r="H74" s="75"/>
+      <c r="I74" s="76"/>
       <c r="J74" s="38"/>
       <c r="K74" s="38"/>
       <c r="L74" s="38"/>
     </row>
     <row r="75" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A75" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="B75" s="63" t="s">
-        <v>82</v>
-      </c>
-      <c r="C75" s="74" t="s">
-        <v>83</v>
-      </c>
+      <c r="A75" s="66"/>
+      <c r="B75" s="73"/>
+      <c r="C75" s="74"/>
       <c r="D75" s="75"/>
       <c r="E75" s="75"/>
       <c r="F75" s="75"/>
-      <c r="G75" s="75">
-        <f>F75*D75</f>
-        <v>0</v>
-      </c>
-      <c r="H75" s="75">
-        <f>F75*E75</f>
-        <v>0</v>
-      </c>
+      <c r="G75" s="75"/>
+      <c r="H75" s="75"/>
       <c r="I75" s="76"/>
-      <c r="J75" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K75" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="L75" s="38" t="s">
-        <v>16</v>
-      </c>
+      <c r="J75" s="38"/>
+      <c r="K75" s="38"/>
+      <c r="L75" s="38"/>
     </row>
     <row r="76" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A76" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="B76" s="63" t="s">
-        <v>66</v>
-      </c>
-      <c r="C76" s="74" t="s">
-        <v>43</v>
-      </c>
+      <c r="A76" s="66"/>
+      <c r="B76" s="73"/>
+      <c r="C76" s="74"/>
       <c r="D76" s="75"/>
       <c r="E76" s="75"/>
       <c r="F76" s="75"/>
-      <c r="G76" s="75">
-        <f>F76*D76</f>
-        <v>0</v>
-      </c>
-      <c r="H76" s="75">
-        <f>F76*E76</f>
-        <v>0</v>
-      </c>
+      <c r="G76" s="75"/>
+      <c r="H76" s="75"/>
       <c r="I76" s="76"/>
-      <c r="J76" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K76" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="L76" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" s="58" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A77" s="66" t="s">
-        <v>10</v>
-      </c>
-      <c r="B77" s="84" t="s">
-        <v>84</v>
-      </c>
-      <c r="C77" s="68"/>
-      <c r="D77" s="69"/>
-      <c r="E77" s="69"/>
-      <c r="F77" s="69"/>
-      <c r="G77" s="69">
-        <f>SUBTOTAL(9,G78:G88)</f>
-        <v>311621</v>
-      </c>
-      <c r="H77" s="69">
-        <f>SUBTOTAL(9,H78:H88)</f>
-        <v>477500</v>
-      </c>
+      <c r="J76" s="38"/>
+      <c r="K76" s="38"/>
+      <c r="L76" s="38"/>
+    </row>
+    <row r="77" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A77" s="66"/>
+      <c r="B77" s="73"/>
+      <c r="C77" s="74"/>
+      <c r="D77" s="75"/>
+      <c r="E77" s="75"/>
+      <c r="F77" s="75"/>
+      <c r="G77" s="75"/>
+      <c r="H77" s="75"/>
       <c r="I77" s="76"/>
       <c r="J77" s="38"/>
       <c r="K77" s="38"/>
       <c r="L77" s="38"/>
     </row>
     <row r="78" spans="1:12" s="58" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A78" s="66" t="s">
-        <v>34</v>
-      </c>
-      <c r="B78" s="67" t="s">
-        <v>85</v>
-      </c>
-      <c r="C78" s="68"/>
+      <c r="A78" s="66"/>
+      <c r="B78" s="67"/>
+      <c r="C78" s="80"/>
       <c r="D78" s="69"/>
       <c r="E78" s="69"/>
-      <c r="F78" s="69"/>
-      <c r="G78" s="69">
-        <f>SUBTOTAL(9,G79:G85)</f>
-        <v>311621</v>
-      </c>
-      <c r="H78" s="69">
-        <f>SUBTOTAL(9,H79:H85)</f>
-        <v>477500</v>
-      </c>
+      <c r="F78" s="85"/>
+      <c r="G78" s="69"/>
+      <c r="H78" s="69"/>
       <c r="I78" s="70"/>
       <c r="J78" s="57"/>
       <c r="K78" s="57"/>
       <c r="L78" s="57"/>
     </row>
-    <row r="79" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A79" s="66" t="s">
-        <v>6</v>
-      </c>
-      <c r="B79" s="73" t="s">
-        <v>86</v>
-      </c>
-      <c r="C79" s="74" t="s">
-        <v>87</v>
-      </c>
+    <row r="79" spans="1:12" s="48" customFormat="1" ht="13.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
+      <c r="A79" s="66"/>
+      <c r="B79" s="73"/>
+      <c r="C79" s="74"/>
       <c r="D79" s="75"/>
-      <c r="E79" s="75">
-        <v>1</v>
-      </c>
-      <c r="F79" s="75">
-        <v>60000</v>
-      </c>
-      <c r="G79" s="75">
-        <f t="shared" ref="G79:G85" si="10">F79*D79</f>
+      <c r="E79" s="75"/>
+      <c r="F79" s="75"/>
+      <c r="G79" s="75"/>
+      <c r="H79" s="75"/>
+      <c r="I79" s="76"/>
+      <c r="J79" s="38"/>
+      <c r="K79" s="38"/>
+      <c r="L79" s="38"/>
+    </row>
+    <row r="80" spans="1:12" s="48" customFormat="1" ht="27.95" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
+      <c r="A80" s="66"/>
+      <c r="B80" s="73"/>
+      <c r="C80" s="74"/>
+      <c r="D80" s="75"/>
+      <c r="E80" s="75"/>
+      <c r="F80" s="75"/>
+      <c r="G80" s="75"/>
+      <c r="H80" s="75"/>
+      <c r="I80" s="76"/>
+      <c r="J80" s="38"/>
+      <c r="K80" s="38"/>
+      <c r="L80" s="38"/>
+    </row>
+    <row r="81" spans="1:12" s="62" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A81" s="70" t="s">
+        <v>37</v>
+      </c>
+      <c r="B81" s="64" t="s">
+        <v>19</v>
+      </c>
+      <c r="C81" s="68"/>
+      <c r="D81" s="69"/>
+      <c r="E81" s="69"/>
+      <c r="F81" s="69"/>
+      <c r="G81" s="69">
+        <f>SUBTOTAL(9,G82:G85)</f>
         <v>0</v>
       </c>
-      <c r="H79" s="75">
-        <f t="shared" ref="H79:H85" si="11">F79*E79</f>
-        <v>60000</v>
-      </c>
-      <c r="I79" s="76"/>
-      <c r="J79" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K79" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="L79" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A80" s="66" t="s">
-        <v>6</v>
-      </c>
-      <c r="B80" s="73" t="s">
-        <v>88</v>
-      </c>
-      <c r="C80" s="74" t="s">
-        <v>87</v>
-      </c>
-      <c r="D80" s="75"/>
-      <c r="E80" s="75">
-        <v>1</v>
-      </c>
-      <c r="F80" s="75">
-        <v>300000</v>
-      </c>
-      <c r="G80" s="75">
-        <f t="shared" si="10"/>
+      <c r="H81" s="69">
+        <f>SUBTOTAL(9,H82:H85)</f>
         <v>0</v>
       </c>
-      <c r="H80" s="75">
-        <f t="shared" si="11"/>
-        <v>300000</v>
-      </c>
-      <c r="I80" s="76"/>
-      <c r="J80" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K80" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="L80" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A81" s="66" t="s">
-        <v>6</v>
-      </c>
-      <c r="B81" s="73" t="s">
-        <v>89</v>
-      </c>
-      <c r="C81" s="74" t="s">
-        <v>87</v>
-      </c>
-      <c r="D81" s="75">
-        <v>1</v>
-      </c>
-      <c r="E81" s="75">
-        <v>1</v>
-      </c>
-      <c r="F81" s="75">
-        <v>100000</v>
-      </c>
-      <c r="G81" s="75">
-        <f t="shared" si="10"/>
-        <v>100000</v>
-      </c>
-      <c r="H81" s="75">
-        <f t="shared" si="11"/>
-        <v>100000</v>
-      </c>
-      <c r="I81" s="76"/>
-      <c r="J81" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K81" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="L81" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A82" s="66" t="s">
-        <v>6</v>
-      </c>
-      <c r="B82" s="73" t="s">
-        <v>90</v>
-      </c>
-      <c r="C82" s="74" t="s">
-        <v>87</v>
-      </c>
-      <c r="D82" s="75">
-        <v>1</v>
-      </c>
-      <c r="E82" s="75">
-        <v>1</v>
-      </c>
-      <c r="F82" s="75">
-        <v>2500</v>
-      </c>
-      <c r="G82" s="75">
-        <f t="shared" si="10"/>
-        <v>2500</v>
-      </c>
-      <c r="H82" s="75">
-        <f t="shared" si="11"/>
-        <v>2500</v>
-      </c>
+      <c r="I81" s="69"/>
+      <c r="J81" s="60"/>
+      <c r="K81" s="61"/>
+      <c r="L81" s="61"/>
+    </row>
+    <row r="82" spans="1:12" s="87" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A82" s="82"/>
+      <c r="B82" s="86"/>
+      <c r="C82" s="74"/>
+      <c r="D82" s="75"/>
+      <c r="E82" s="75"/>
+      <c r="F82" s="75"/>
+      <c r="G82" s="75"/>
+      <c r="H82" s="75"/>
       <c r="I82" s="76"/>
-      <c r="J82" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K82" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="L82" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A83" s="66" t="s">
-        <v>6</v>
-      </c>
-      <c r="B83" s="73" t="s">
-        <v>91</v>
-      </c>
-      <c r="C83" s="74" t="s">
-        <v>87</v>
-      </c>
+      <c r="J82" s="38"/>
+      <c r="K82" s="61"/>
+      <c r="L82" s="61"/>
+    </row>
+    <row r="83" spans="1:12" s="87" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A83" s="82"/>
+      <c r="B83" s="86"/>
+      <c r="C83" s="74"/>
       <c r="D83" s="75"/>
-      <c r="E83" s="75">
-        <v>1</v>
-      </c>
-      <c r="F83" s="75">
-        <v>15000</v>
-      </c>
-      <c r="G83" s="75">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="H83" s="75">
-        <f t="shared" si="11"/>
-        <v>15000</v>
-      </c>
+      <c r="E83" s="75"/>
+      <c r="F83" s="75"/>
+      <c r="G83" s="75"/>
+      <c r="H83" s="75"/>
       <c r="I83" s="76"/>
-      <c r="J83" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K83" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="L83" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A84" s="66" t="s">
-        <v>6</v>
-      </c>
-      <c r="B84" s="73" t="s">
-        <v>92</v>
-      </c>
-      <c r="C84" s="74" t="s">
-        <v>87</v>
-      </c>
-      <c r="D84" s="75">
-        <v>1</v>
-      </c>
+      <c r="J83" s="38"/>
+      <c r="K83" s="61"/>
+      <c r="L83" s="61"/>
+    </row>
+    <row r="84" spans="1:12" s="87" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A84" s="82"/>
+      <c r="B84" s="86"/>
+      <c r="C84" s="74"/>
+      <c r="D84" s="75"/>
       <c r="E84" s="75"/>
-      <c r="F84" s="75">
-        <v>74121</v>
-      </c>
-      <c r="G84" s="75">
-        <f t="shared" si="10"/>
-        <v>74121</v>
-      </c>
-      <c r="H84" s="75">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
+      <c r="F84" s="75"/>
+      <c r="G84" s="75"/>
+      <c r="H84" s="75"/>
       <c r="I84" s="76"/>
-      <c r="J84" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K84" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="L84" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A85" s="66" t="s">
-        <v>6</v>
-      </c>
-      <c r="B85" s="73" t="s">
-        <v>93</v>
-      </c>
-      <c r="C85" s="74" t="s">
-        <v>94</v>
-      </c>
-      <c r="D85" s="75">
-        <v>1</v>
-      </c>
+      <c r="J84" s="38"/>
+      <c r="K84" s="61"/>
+      <c r="L84" s="61"/>
+    </row>
+    <row r="85" spans="1:12" s="87" customFormat="1" ht="13.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A85" s="82"/>
+      <c r="B85" s="86"/>
+      <c r="C85" s="74"/>
+      <c r="D85" s="75"/>
       <c r="E85" s="75"/>
-      <c r="F85" s="75">
-        <v>135000</v>
-      </c>
-      <c r="G85" s="75">
-        <f t="shared" si="10"/>
-        <v>135000</v>
-      </c>
-      <c r="H85" s="75">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
+      <c r="F85" s="75"/>
+      <c r="G85" s="75"/>
+      <c r="H85" s="75"/>
       <c r="I85" s="76"/>
-      <c r="J85" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K85" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="L85" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" s="58" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A86" s="66" t="s">
-        <v>40</v>
-      </c>
-      <c r="B86" s="67" t="s">
-        <v>95</v>
-      </c>
-      <c r="C86" s="80"/>
-      <c r="D86" s="69"/>
-      <c r="E86" s="69"/>
-      <c r="F86" s="85"/>
-      <c r="G86" s="69">
-        <f>SUBTOTAL(9,G87:G88)</f>
-        <v>0</v>
-      </c>
-      <c r="H86" s="69">
-        <f>SUBTOTAL(9,H87:H88)</f>
-        <v>0</v>
-      </c>
-      <c r="I86" s="70"/>
-      <c r="J86" s="57"/>
-      <c r="K86" s="57"/>
-      <c r="L86" s="57"/>
-    </row>
-    <row r="87" spans="1:12" s="48" customFormat="1" ht="14.1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A87" s="66" t="s">
-        <v>6</v>
-      </c>
-      <c r="B87" s="73" t="s">
-        <v>96</v>
-      </c>
-      <c r="C87" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="D87" s="75"/>
-      <c r="E87" s="75"/>
-      <c r="F87" s="75"/>
-      <c r="G87" s="75">
-        <f>F87*D87</f>
-        <v>0</v>
-      </c>
-      <c r="H87" s="75">
-        <f>F87*E87</f>
-        <v>0</v>
-      </c>
-      <c r="I87" s="76"/>
-      <c r="J87" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K87" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="L87" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" s="48" customFormat="1" ht="27.95" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
-      <c r="A88" s="66" t="s">
-        <v>6</v>
-      </c>
-      <c r="B88" s="73" t="s">
-        <v>97</v>
-      </c>
-      <c r="C88" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="D88" s="75"/>
-      <c r="E88" s="75"/>
-      <c r="F88" s="75"/>
-      <c r="G88" s="75">
-        <f>F88*D88</f>
-        <v>0</v>
-      </c>
-      <c r="H88" s="75">
-        <f>F88*E88</f>
-        <v>0</v>
-      </c>
-      <c r="I88" s="76"/>
-      <c r="J88" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K88" s="38" t="s">
-        <v>25</v>
-      </c>
-      <c r="L88" s="38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" s="62" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A89" s="70" t="s">
-        <v>98</v>
-      </c>
-      <c r="B89" s="64" t="s">
-        <v>26</v>
-      </c>
-      <c r="C89" s="68"/>
-      <c r="D89" s="69"/>
-      <c r="E89" s="69"/>
-      <c r="F89" s="69"/>
-      <c r="G89" s="69">
-        <f>SUBTOTAL(9,G90:G93)</f>
-        <v>223800</v>
-      </c>
-      <c r="H89" s="69">
-        <f>SUBTOTAL(9,H90:H93)</f>
-        <v>223800</v>
-      </c>
-      <c r="I89" s="69"/>
-      <c r="J89" s="60"/>
-      <c r="K89" s="61"/>
-      <c r="L89" s="61"/>
-    </row>
-    <row r="90" spans="1:12" s="87" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A90" s="82" t="s">
-        <v>34</v>
-      </c>
-      <c r="B90" s="86" t="s">
-        <v>99</v>
-      </c>
-      <c r="C90" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="D90" s="75">
-        <v>12</v>
-      </c>
-      <c r="E90" s="75">
-        <v>12</v>
-      </c>
-      <c r="F90" s="75">
-        <v>4700</v>
-      </c>
-      <c r="G90" s="75">
-        <f>F90*D90</f>
-        <v>56400</v>
-      </c>
-      <c r="H90" s="75">
-        <f>F90*E90</f>
-        <v>56400</v>
-      </c>
-      <c r="I90" s="76"/>
-      <c r="J90" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K90" s="61" t="s">
-        <v>27</v>
-      </c>
-      <c r="L90" s="61" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" s="87" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A91" s="82" t="s">
-        <v>40</v>
-      </c>
-      <c r="B91" s="86" t="s">
-        <v>100</v>
-      </c>
-      <c r="C91" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="D91" s="75">
-        <v>15</v>
-      </c>
-      <c r="E91" s="75">
-        <v>15</v>
-      </c>
-      <c r="F91" s="75">
-        <v>3700</v>
-      </c>
-      <c r="G91" s="75">
-        <f>F91*D91</f>
-        <v>55500</v>
-      </c>
-      <c r="H91" s="75">
-        <f>F91*E91</f>
-        <v>55500</v>
-      </c>
-      <c r="I91" s="76"/>
-      <c r="J91" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K91" s="61" t="s">
-        <v>27</v>
-      </c>
-      <c r="L91" s="61" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" s="87" customFormat="1" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A92" s="82" t="s">
-        <v>44</v>
-      </c>
-      <c r="B92" s="86" t="s">
-        <v>101</v>
-      </c>
-      <c r="C92" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="D92" s="75">
-        <v>12</v>
-      </c>
-      <c r="E92" s="75">
-        <v>12</v>
-      </c>
-      <c r="F92" s="75">
-        <v>4700</v>
-      </c>
-      <c r="G92" s="75">
-        <f>F92*D92</f>
-        <v>56400</v>
-      </c>
-      <c r="H92" s="75">
-        <f>F92*E92</f>
-        <v>56400</v>
-      </c>
-      <c r="I92" s="76"/>
-      <c r="J92" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K92" s="61" t="s">
-        <v>27</v>
-      </c>
-      <c r="L92" s="61" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" s="87" customFormat="1" ht="13.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A93" s="82" t="s">
-        <v>47</v>
-      </c>
-      <c r="B93" s="86" t="s">
-        <v>102</v>
-      </c>
-      <c r="C93" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="D93" s="75">
-        <v>15</v>
-      </c>
-      <c r="E93" s="75">
-        <v>15</v>
-      </c>
-      <c r="F93" s="75">
-        <v>3700</v>
-      </c>
-      <c r="G93" s="75">
-        <f>F93*D93</f>
-        <v>55500</v>
-      </c>
-      <c r="H93" s="75">
-        <f>F93*E93</f>
-        <v>55500</v>
-      </c>
-      <c r="I93" s="76"/>
-      <c r="J93" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="K93" s="61" t="s">
-        <v>27</v>
-      </c>
-      <c r="L93" s="61" t="s">
-        <v>16</v>
-      </c>
+      <c r="J85" s="38"/>
+      <c r="K85" s="61"/>
+      <c r="L85" s="61"/>
     </row>
   </sheetData>
-  <autoFilter ref="A7:Q93"/>
+  <autoFilter ref="A7:Q85"/>
   <dataConsolidate/>
   <mergeCells count="12">
     <mergeCell ref="P1:P7"/>
@@ -5841,31 +4194,12 @@
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="G4:H5"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L14 L1:L11 K10:K16 J1:J16">
+      <formula1>#REF!</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.4" right="0" top="0.28000000000000003" bottom="0" header="0.1" footer="0"/>
   <pageSetup paperSize="8" scale="85" fitToHeight="0" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>L14 L1:L11</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>J1:J16</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>K10:K16</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>